--- a/Data/Raw/wa_local.xlsx
+++ b/Data/Raw/wa_local.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\WA-FEWP\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAF0DA6-F524-4554-9557-C1309F89CBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3112D00-1634-4EC9-BB13-D8A4AFDA56F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="1357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="1357">
   <si>
     <t>waID</t>
   </si>
@@ -20437,6 +20437,9 @@
       <c r="P215" t="s">
         <v>1356</v>
       </c>
+      <c r="Q215" t="s">
+        <v>129</v>
+      </c>
       <c r="R215" t="s">
         <v>1339</v>
       </c>

--- a/Data/Raw/wa_local.xlsx
+++ b/Data/Raw/wa_local.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\WA-FEWP\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3112D00-1634-4EC9-BB13-D8A4AFDA56F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218214FE-4FBC-4784-99AA-052D1DB4F649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="1357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3602" uniqueCount="1358">
   <si>
     <t>waID</t>
   </si>
@@ -4142,6 +4142,9 @@
   </si>
   <si>
     <t>King County Sheriff's Office, Burien Police Department, Lakewood Police Department</t>
+  </si>
+  <si>
+    <t>Marvin Oliva Medina</t>
   </si>
 </sst>
 </file>
@@ -20407,6 +20410,15 @@
       <c r="A215">
         <v>90218</v>
       </c>
+      <c r="B215">
+        <v>19193</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E215">
+        <v>34</v>
+      </c>
       <c r="F215" t="s">
         <v>31</v>
       </c>

--- a/Data/Raw/wa_local.xlsx
+++ b/Data/Raw/wa_local.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\WA-FEWP\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543F5B52-D00F-4E3E-84E8-5DF82F9B7B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F78ACF-B2E3-49DF-BD23-9240ECA0928F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="1590" windowWidth="19185" windowHeight="11265" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
   </bookViews>
   <sheets>
     <sheet name="names" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3534" uniqueCount="1432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3621" uniqueCount="1470">
   <si>
     <t>waID</t>
   </si>
@@ -4339,9 +4339,6 @@
     <t>Subject; Passenger</t>
   </si>
   <si>
-    <t>WSP patrol pursued a suspected stolen vehicle at speeds over 100 MPH.  The vehicle lost control and crashed, killing a passenger, and seriously injuring the driver and another passenger</t>
-  </si>
-  <si>
     <t>https://komonews.com/news/local/one-person-killed-after-driver-in-stolen-car-crashes-at-110-mph-while-evading-troopers</t>
   </si>
   <si>
@@ -4354,9 +4351,6 @@
     <t>https://www.southwhidbeyrecord.com/news/oak-harbor-man-killed-by-police-identified/</t>
   </si>
   <si>
-    <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://snohomishcountywa.gov/DocumentCenter/View/141669/2026-01-15pdf</t>
-  </si>
-  <si>
     <t>https://komonews.com/news/local/kidnapping-victim-recounts-ordeal-with-armed-domestic-violence-suspect-on-the-run</t>
   </si>
   <si>
@@ -4367,6 +4361,126 @@
   </si>
   <si>
     <t>Multiple agencies</t>
+  </si>
+  <si>
+    <t>4600 45th Ave SE</t>
+  </si>
+  <si>
+    <t>Police responded to a reported disturbance.  After they arrived the man allegedly fired shots and was barricading himself in the apartment.  The regional SWAT was called in.  The man allegedly came out and raised his gun, and the police shot and killed him.</t>
+  </si>
+  <si>
+    <t>Lacey Police Department, Regional SWAT</t>
+  </si>
+  <si>
+    <t>https://oii.wa.gov/news-and-updates/2026/update-oii-investigating-deadly-force-incident-involving-lacey-pd-sets-tip-line</t>
+  </si>
+  <si>
+    <t>112 Park Avenue South</t>
+  </si>
+  <si>
+    <t>Pierce County Sheriff's Department</t>
+  </si>
+  <si>
+    <t>A man called 911 to report he had been stabbed. Deputies arrived to learn that an unknown man had approached the victim and asked about his religious beliefs.  Deputies found the suspect and attempted to talk to him. The man was allegedly armed and advanced on the deputies, so they shot and killed him.</t>
+  </si>
+  <si>
+    <t>https://www.thenewstribune.com/news/local/article314449249.html</t>
+  </si>
+  <si>
+    <t>https://snohomishcountywa.gov/DocumentCenter/View/141669/2026-01-15pdf</t>
+  </si>
+  <si>
+    <t>Kaleb Lewis</t>
+  </si>
+  <si>
+    <t>https://www.chronline.com/stories/oii-identifies-officer-who-killed-armed-man-during-a-standoff-in-lacey,395380</t>
+  </si>
+  <si>
+    <t>Officer David MacLurg</t>
+  </si>
+  <si>
+    <t>race coded from https://www.king5.com/article/news/local/family-identifies-man-killed-lacey-apartment-standoff/281-9dba8a18-87d8-47e1-8149-9fa8684db301</t>
+  </si>
+  <si>
+    <t>Alrico Ray Coleman</t>
+  </si>
+  <si>
+    <t>https://www.yahoo.com/news/articles/tacoma-man-fatally-shot-deputies-210314185.html</t>
+  </si>
+  <si>
+    <t>https://www.king5.com/article/news/local/driver-hit-suspect-fleeing-from-wsp-trooper-dies/281-9ae9bf88-2391-4a8c-b9b3-5b9a05acec00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gayle Robin Horner</t>
+  </si>
+  <si>
+    <t>A trooper attempted to pull over a vehicle in Tacoma and the suspect driver did not stop. The driver then crashed into another vehicle and caught fire.  The driver of the other car, a 74 year old woman, was killed.</t>
+  </si>
+  <si>
+    <t>from addl url, claim that the pursuit was terminated before accident:  The tragic incident began around 9:15 p.m. on State Route 7 when a Washington State Patrol trooper noticed a Toyota Corolla swerving between lanes and driving onto turn lane lines. The car eventually stopped at a red light on South 72nd Street, and the trooper approached the driver, who reportedly smelled of alcohol and had bloodshot, watery eyes.  When asked for his license, the driver said he didn’t have one. As the trooper told him to stop the vehicle, the driver suddenly sped off. The trooper gave chase for a short time but turned off his emergency lights and continued east along South 72nd Street.</t>
+  </si>
+  <si>
+    <t>https://www.thenewstribune.com/news/local/crime/article314264368.html</t>
+  </si>
+  <si>
+    <t>7200 E McKinley Ave</t>
+  </si>
+  <si>
+    <t>https://medis-public.piercecountywa.gov/app/v2/case/detail/56635</t>
+  </si>
+  <si>
+    <t>https://medis-public.piercecountywa.gov/app/v2/case/detail/56820</t>
+  </si>
+  <si>
+    <t>Serenity Rose Upchurch</t>
+  </si>
+  <si>
+    <t>WSP patrol pursued a suspected stolen vehicle at speeds over 100 MPH.  The vehicle lost control and crashed, killing a passenger, and seriously injured the driver and another passenger</t>
+  </si>
+  <si>
+    <t>https://www.thenewstribune.com/news/local/crime/article314391814.html</t>
+  </si>
+  <si>
+    <t>Ryan Cole</t>
+  </si>
+  <si>
+    <t>https://www.piercecountywa.gov/m/newsflash/Home/Detail/7030</t>
+  </si>
+  <si>
+    <t>Incident is not listed in the PCME news releases</t>
+  </si>
+  <si>
+    <t>Maria C. Mendoza</t>
+  </si>
+  <si>
+    <t>Interstate 182 near milepost 12</t>
+  </si>
+  <si>
+    <t>Police attempted to stop a vehicle after the driver showed signs of impairment, but the driver fled, prompting a pursuit, authorities said.  According to the Washington State Patrol, the subject’s vehicle was traveling westbound on I-182 when it lost control, left the roadway, and rolled over a cable barrier into the eastbound lanes and struck an oncoming car traveling eastbound, troopers said.  The driver of the struck vehicle was pronounced dead at the scene.</t>
+  </si>
+  <si>
+    <t>https://keprtv.com/news/local/woman-killed-in-pasco-crash-during-police-pursuit-teen-driver-in-custody</t>
+  </si>
+  <si>
+    <t>https://www.applevalleynewsnow.com/news/grandview-woman-dies-in-police-pursuit-crash-in-pasco/article_912228b6-968f-474f-945f-b75bd6b062d1.html</t>
+  </si>
+  <si>
+    <t>33000 First Ave S</t>
+  </si>
+  <si>
+    <t>Officers were called around 8:45 a.m. to reports of a car sitting in the middle of the road , and a man passed out behind the driver seat.  Police allegedly determined the car was stolen, and when they went to contact the suspect, he got out of the car and ran.  The man, who allegedly had a firearm and tried to carjack a person driving by, was shot and killed by officers.</t>
+  </si>
+  <si>
+    <t>https://www.fox13seattle.com/news/man-shot-killed-federal-way-police</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Branden Bouathet  Chindavong</t>
+  </si>
+  <si>
+    <t>15941/19905</t>
+  </si>
+  <si>
+    <t>https://content.govdelivery.com/attachments/WAKING/2026/02/09/file_attachments/3549182/Decedents%20List_02092026.pdf</t>
   </si>
 </sst>
 </file>
@@ -4494,13 +4608,13 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4814,10 +4928,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}" name="Table2" displayName="Table2" ref="A1:AI225" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A1:AI225" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI224">
-    <sortCondition ref="A1:A224"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}" name="Table2" displayName="Table2" ref="A1:AI230" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A1:AI230" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI230">
+    <sortCondition ref="A1:A230"/>
   </sortState>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{C24056F2-460B-462C-AD5F-7EC8949E9151}" name="waID" dataDxfId="34"/>
@@ -5157,7 +5271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A26517-14A9-4E8E-8064-5F228E1B70B4}">
-  <dimension ref="A1:AI250"/>
+  <dimension ref="A1:AI249"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="7.28515625" customWidth="1"/>
@@ -5166,6 +5280,7 @@
     <col min="6" max="6" width="9.42578125" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.140625" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" customWidth="1"/>
@@ -5183,7 +5298,7 @@
     <col min="30" max="30" width="15.85546875" customWidth="1"/>
     <col min="31" max="31" width="12.42578125" customWidth="1"/>
     <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="34" max="34" width="9.28515625" customWidth="1"/>
+    <col min="34" max="34" width="22.7109375" customWidth="1"/>
     <col min="35" max="35" width="9.140625" style="13"/>
   </cols>
   <sheetData>
@@ -15242,70 +15357,87 @@
       </c>
     </row>
     <row r="145" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="14">
+      <c r="A145">
         <v>90146</v>
       </c>
-      <c r="B145" s="14">
+      <c r="B145">
         <v>16405</v>
       </c>
-      <c r="E145" s="15">
+      <c r="C145"/>
+      <c r="D145" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E145" s="11">
         <v>45705</v>
       </c>
-      <c r="F145" s="14">
+      <c r="F145">
         <v>45</v>
       </c>
-      <c r="G145" s="14" t="s">
+      <c r="G145" t="s">
         <v>30</v>
       </c>
-      <c r="I145" s="14" t="s">
+      <c r="H145"/>
+      <c r="I145" t="s">
         <v>516</v>
       </c>
-      <c r="J145" s="14" t="s">
+      <c r="J145" t="s">
         <v>517</v>
       </c>
-      <c r="K145" s="14">
+      <c r="K145">
         <v>98373</v>
       </c>
-      <c r="L145" s="14" t="s">
+      <c r="L145" t="s">
         <v>395</v>
       </c>
-      <c r="M145" s="14">
+      <c r="M145">
         <v>47.140076499999999</v>
       </c>
-      <c r="N145" s="14">
+      <c r="N145">
         <v>-122.46689670000001</v>
       </c>
-      <c r="O145" s="14" t="s">
+      <c r="O145" t="s">
         <v>416</v>
       </c>
-      <c r="P145" s="14" t="s">
+      <c r="P145" t="s">
         <v>126</v>
       </c>
-      <c r="Q145" s="14" t="s">
+      <c r="Q145" t="s">
         <v>127</v>
       </c>
-      <c r="R145" s="14" t="s">
+      <c r="R145" t="s">
         <v>147</v>
       </c>
-      <c r="X145" s="14" t="s">
+      <c r="S145"/>
+      <c r="T145"/>
+      <c r="U145"/>
+      <c r="V145"/>
+      <c r="W145"/>
+      <c r="X145" t="s">
         <v>126</v>
       </c>
-      <c r="Z145" s="14" t="s">
+      <c r="Y145"/>
+      <c r="Z145" t="s">
         <v>518</v>
       </c>
-      <c r="AA145" s="14" t="s">
+      <c r="AA145" t="s">
         <v>519</v>
       </c>
-      <c r="AC145" s="14" t="s">
+      <c r="AB145" t="s">
+        <v>520</v>
+      </c>
+      <c r="AC145" t="s">
         <v>519</v>
       </c>
-      <c r="AD145" s="14" t="s">
+      <c r="AD145" t="s">
         <v>88</v>
       </c>
-      <c r="AH145" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="AI145" s="16"/>
+      <c r="AE145"/>
+      <c r="AF145"/>
+      <c r="AG145"/>
+      <c r="AH145" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AI145" s="13"/>
     </row>
     <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146">
@@ -18094,6 +18226,9 @@
       <c r="AA185" s="14" t="s">
         <v>626</v>
       </c>
+      <c r="AB185" s="14" t="s">
+        <v>1458</v>
+      </c>
       <c r="AD185" s="14" t="s">
         <v>88</v>
       </c>
@@ -18103,8 +18238,8 @@
       <c r="A186" s="14">
         <v>90189</v>
       </c>
-      <c r="B186" s="14">
-        <v>15941</v>
+      <c r="B186" s="14" t="s">
+        <v>1468</v>
       </c>
       <c r="C186" s="14">
         <v>1</v>
@@ -20741,11 +20876,20 @@
       <c r="A224">
         <v>90227</v>
       </c>
+      <c r="B224">
+        <v>20258</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1453</v>
+      </c>
       <c r="E224" s="11">
         <v>46040</v>
       </c>
+      <c r="F224">
+        <v>17</v>
+      </c>
       <c r="G224" t="s">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="H224"/>
       <c r="I224" t="s">
@@ -20788,113 +20932,475 @@
         <v>126</v>
       </c>
       <c r="Z224" t="s">
+        <v>1454</v>
+      </c>
+      <c r="AA224" t="s">
         <v>1422</v>
       </c>
-      <c r="AA224" t="s">
+      <c r="AC224" t="s">
+        <v>1455</v>
+      </c>
+      <c r="AH224" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="225" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>90228</v>
+      </c>
+      <c r="B225">
+        <v>19798</v>
+      </c>
+      <c r="D225" s="19" t="s">
         <v>1423</v>
       </c>
-    </row>
-    <row r="225" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A225" s="19">
-        <v>90228</v>
-      </c>
-      <c r="B225" s="19"/>
-      <c r="C225" s="19"/>
-      <c r="D225" s="22" t="s">
+      <c r="E225" s="11">
+        <v>46024</v>
+      </c>
+      <c r="F225">
+        <v>38</v>
+      </c>
+      <c r="G225" t="s">
+        <v>30</v>
+      </c>
+      <c r="H225" t="s">
+        <v>77</v>
+      </c>
+      <c r="I225" t="s">
+        <v>1428</v>
+      </c>
+      <c r="J225" t="s">
+        <v>1102</v>
+      </c>
+      <c r="K225">
+        <v>98203</v>
+      </c>
+      <c r="L225" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M225">
+        <v>47.942715300000003</v>
+      </c>
+      <c r="N225">
+        <v>-122.2219331</v>
+      </c>
+      <c r="O225" t="s">
+        <v>1429</v>
+      </c>
+      <c r="P225" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>37</v>
+      </c>
+      <c r="R225" t="s">
+        <v>61</v>
+      </c>
+      <c r="V225" t="s">
+        <v>38</v>
+      </c>
+      <c r="W225" t="s">
+        <v>39</v>
+      </c>
+      <c r="X225" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z225" t="s">
         <v>1424</v>
       </c>
-      <c r="E225" s="20">
-        <v>46024</v>
-      </c>
-      <c r="F225" s="19">
-        <v>38</v>
-      </c>
-      <c r="G225" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="H225" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="I225" s="19" t="s">
-        <v>1430</v>
-      </c>
-      <c r="J225" s="19" t="s">
-        <v>1102</v>
-      </c>
-      <c r="K225" s="19">
-        <v>98203</v>
-      </c>
-      <c r="L225" s="19" t="s">
-        <v>1081</v>
-      </c>
-      <c r="M225" s="19">
-        <v>47.942715300000003</v>
-      </c>
-      <c r="N225" s="19">
-        <v>-122.2219331</v>
-      </c>
-      <c r="O225" s="19" t="s">
-        <v>1431</v>
-      </c>
-      <c r="P225" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q225" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="R225" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="S225" s="19"/>
-      <c r="T225" s="19"/>
-      <c r="U225" s="19"/>
-      <c r="V225" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="W225" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="X225" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y225" s="19"/>
-      <c r="Z225" s="19" t="s">
+      <c r="AA225" s="18" t="s">
         <v>1425</v>
       </c>
-      <c r="AA225" s="18" t="s">
+      <c r="AB225" s="18" t="s">
+        <v>1427</v>
+      </c>
+      <c r="AC225" s="18" t="s">
         <v>1426</v>
       </c>
-      <c r="AB225" s="18" t="s">
-        <v>1429</v>
-      </c>
-      <c r="AC225" s="18" t="s">
-        <v>1428</v>
-      </c>
-      <c r="AD225" s="19"/>
-      <c r="AE225" s="19"/>
-      <c r="AF225" s="19"/>
       <c r="AG225" s="18" t="s">
         <v>1279</v>
       </c>
-      <c r="AH225" s="19" t="s">
-        <v>1427</v>
-      </c>
-      <c r="AI225" s="21"/>
+      <c r="AH225" s="18" t="s">
+        <v>1438</v>
+      </c>
     </row>
     <row r="226" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="H226"/>
+      <c r="A226">
+        <v>90229</v>
+      </c>
+      <c r="B226">
+        <v>20345</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E226" s="11">
+        <v>46043</v>
+      </c>
+      <c r="F226">
+        <v>30</v>
+      </c>
+      <c r="G226" t="s">
+        <v>30</v>
+      </c>
+      <c r="H226" t="s">
+        <v>31</v>
+      </c>
+      <c r="I226" t="s">
+        <v>1430</v>
+      </c>
+      <c r="J226" t="s">
+        <v>434</v>
+      </c>
+      <c r="K226">
+        <v>98503</v>
+      </c>
+      <c r="L226" t="s">
+        <v>348</v>
+      </c>
+      <c r="M226">
+        <v>47.007158599999997</v>
+      </c>
+      <c r="N226">
+        <v>-122.82555120000001</v>
+      </c>
+      <c r="O226" t="s">
+        <v>1432</v>
+      </c>
+      <c r="P226" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>37</v>
+      </c>
+      <c r="V226" t="s">
+        <v>38</v>
+      </c>
+      <c r="W226" t="s">
+        <v>39</v>
+      </c>
+      <c r="X226" t="s">
+        <v>1338</v>
+      </c>
+      <c r="Z226" t="s">
+        <v>1431</v>
+      </c>
+      <c r="AA226" s="18" t="s">
+        <v>1440</v>
+      </c>
+      <c r="AB226" t="s">
+        <v>1442</v>
+      </c>
+      <c r="AD226" t="s">
+        <v>1441</v>
+      </c>
+      <c r="AG226" s="18" t="s">
+        <v>1433</v>
+      </c>
     </row>
     <row r="227" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="H227"/>
+      <c r="A227">
+        <v>90230</v>
+      </c>
+      <c r="B227">
+        <v>20444</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E227" s="11">
+        <v>46047</v>
+      </c>
+      <c r="F227">
+        <v>34</v>
+      </c>
+      <c r="G227" t="s">
+        <v>30</v>
+      </c>
+      <c r="H227" t="s">
+        <v>69</v>
+      </c>
+      <c r="I227" t="s">
+        <v>1434</v>
+      </c>
+      <c r="J227" t="s">
+        <v>504</v>
+      </c>
+      <c r="K227">
+        <v>98444</v>
+      </c>
+      <c r="L227" t="s">
+        <v>395</v>
+      </c>
+      <c r="M227">
+        <v>47.155445899999997</v>
+      </c>
+      <c r="N227">
+        <v>-122.44213070000001</v>
+      </c>
+      <c r="O227" t="s">
+        <v>1435</v>
+      </c>
+      <c r="P227" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>37</v>
+      </c>
+      <c r="V227" t="s">
+        <v>38</v>
+      </c>
+      <c r="W227" t="s">
+        <v>119</v>
+      </c>
+      <c r="X227" t="s">
+        <v>1338</v>
+      </c>
+      <c r="Z227" t="s">
+        <v>1436</v>
+      </c>
+      <c r="AA227" s="18" t="s">
+        <v>1437</v>
+      </c>
+      <c r="AC227" s="12" t="s">
+        <v>1444</v>
+      </c>
     </row>
     <row r="228" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="H228"/>
+      <c r="A228">
+        <v>90231</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E228" s="11">
+        <v>46021</v>
+      </c>
+      <c r="F228">
+        <v>74</v>
+      </c>
+      <c r="G228" t="s">
+        <v>158</v>
+      </c>
+      <c r="H228" t="s">
+        <v>31</v>
+      </c>
+      <c r="I228" t="s">
+        <v>1450</v>
+      </c>
+      <c r="J228" t="s">
+        <v>538</v>
+      </c>
+      <c r="K228">
+        <v>98404</v>
+      </c>
+      <c r="L228" t="s">
+        <v>395</v>
+      </c>
+      <c r="M228">
+        <v>47.191805299999999</v>
+      </c>
+      <c r="N228">
+        <v>-122.42360499999999</v>
+      </c>
+      <c r="O228" t="s">
+        <v>125</v>
+      </c>
+      <c r="P228" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>240</v>
+      </c>
+      <c r="R228" t="s">
+        <v>377</v>
+      </c>
+      <c r="S228" t="s">
+        <v>1286</v>
+      </c>
+      <c r="T228" t="s">
+        <v>1287</v>
+      </c>
+      <c r="X228" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z228" t="s">
+        <v>1447</v>
+      </c>
+      <c r="AA228" s="18" t="s">
+        <v>1445</v>
+      </c>
+      <c r="AB228" t="s">
+        <v>1448</v>
+      </c>
+      <c r="AC228" t="s">
+        <v>1449</v>
+      </c>
+      <c r="AH228" t="s">
+        <v>1451</v>
+      </c>
     </row>
     <row r="229" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="H229"/>
+      <c r="A229">
+        <v>90232</v>
+      </c>
+      <c r="B229" s="20">
+        <v>20639</v>
+      </c>
+      <c r="C229" s="20"/>
+      <c r="D229" s="20" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E229" s="21">
+        <v>46059</v>
+      </c>
+      <c r="F229" s="20">
+        <v>57</v>
+      </c>
+      <c r="G229" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H229" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I229" s="20" t="s">
+        <v>1460</v>
+      </c>
+      <c r="J229" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="K229" s="20">
+        <v>99301</v>
+      </c>
+      <c r="L229" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="M229" s="20">
+        <v>46.269905700000002</v>
+      </c>
+      <c r="N229" s="20">
+        <v>-119.2355493</v>
+      </c>
+      <c r="O229" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="P229" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q229" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="R229" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="S229" s="20" t="s">
+        <v>1286</v>
+      </c>
+      <c r="T229" s="20"/>
+      <c r="U229" s="20"/>
+      <c r="V229" s="20"/>
+      <c r="W229" s="20"/>
+      <c r="X229" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y229" s="20"/>
+      <c r="Z229" s="20" t="s">
+        <v>1461</v>
+      </c>
+      <c r="AA229" s="20" t="s">
+        <v>1463</v>
+      </c>
+      <c r="AB229" s="20"/>
+      <c r="AC229" s="18" t="s">
+        <v>1462</v>
+      </c>
+      <c r="AD229" s="20"/>
+      <c r="AE229" s="20"/>
+      <c r="AF229" s="20"/>
+      <c r="AG229" s="20"/>
+      <c r="AH229" s="20"/>
+      <c r="AI229" s="22"/>
     </row>
     <row r="230" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="H230"/>
+      <c r="A230">
+        <v>90233</v>
+      </c>
+      <c r="B230" s="20">
+        <v>20626</v>
+      </c>
+      <c r="C230" s="20"/>
+      <c r="D230" s="20" t="s">
+        <v>1467</v>
+      </c>
+      <c r="E230" s="21">
+        <v>46059</v>
+      </c>
+      <c r="F230" s="20">
+        <v>37</v>
+      </c>
+      <c r="G230" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H230" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="I230" s="20" t="s">
+        <v>1464</v>
+      </c>
+      <c r="J230" s="20" t="s">
+        <v>686</v>
+      </c>
+      <c r="K230" s="20">
+        <v>98003</v>
+      </c>
+      <c r="L230" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="M230" s="20">
+        <v>47.3067487</v>
+      </c>
+      <c r="N230" s="20">
+        <v>-122.3367776</v>
+      </c>
+      <c r="O230" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="P230" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q230" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="R230" s="20"/>
+      <c r="S230" s="20"/>
+      <c r="T230" s="20"/>
+      <c r="U230" s="20"/>
+      <c r="V230" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="W230" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="X230" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y230" s="20"/>
+      <c r="Z230" s="20" t="s">
+        <v>1465</v>
+      </c>
+      <c r="AA230" s="20" t="s">
+        <v>1466</v>
+      </c>
+      <c r="AB230" s="20"/>
+      <c r="AC230" s="20"/>
+      <c r="AD230" s="20"/>
+      <c r="AE230" s="20"/>
+      <c r="AF230" s="20"/>
+      <c r="AG230" s="20"/>
+      <c r="AH230" s="18" t="s">
+        <v>1469</v>
+      </c>
+      <c r="AI230" s="22"/>
     </row>
     <row r="231" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H231"/>
@@ -20952,9 +21458,6 @@
     </row>
     <row r="249" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H249"/>
-    </row>
-    <row r="250" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H250"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -20964,11 +21467,19 @@
     <hyperlink ref="AG225" r:id="rId4" xr:uid="{2C519260-9235-431D-9523-F0D74315F00D}"/>
     <hyperlink ref="AC225" r:id="rId5" xr:uid="{A466EAC4-4C13-46F7-90E0-EC5CBBE7BD51}"/>
     <hyperlink ref="AB225" r:id="rId6" xr:uid="{F2953FD6-0A50-4FC0-833F-04C10310633F}"/>
+    <hyperlink ref="AA226" r:id="rId7" xr:uid="{65B7FDB3-09FD-4CAE-B9C9-70F7F2621DF9}"/>
+    <hyperlink ref="AG226" r:id="rId8" xr:uid="{484813EB-D62B-4B70-ACF4-34108F8588F4}"/>
+    <hyperlink ref="AA227" r:id="rId9" xr:uid="{6B1715B8-CDCF-4189-BF89-E001B1F17FBD}"/>
+    <hyperlink ref="AH225" r:id="rId10" xr:uid="{6843E87A-BF3C-47D7-905C-938B142E1921}"/>
+    <hyperlink ref="AC227" r:id="rId11" xr:uid="{83300A35-257E-4F14-936B-2527AE7EA39A}"/>
+    <hyperlink ref="AA228" r:id="rId12" xr:uid="{B1EC3581-4906-4044-A05B-2D259FBA0E7E}"/>
+    <hyperlink ref="AC229" r:id="rId13" xr:uid="{01A2C460-5A5B-400A-98AC-2BF42B651DEC}"/>
+    <hyperlink ref="AH230" r:id="rId14" xr:uid="{771FF646-43C9-4E59-85CA-18A328886EF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Data/Raw/wa_local.xlsx
+++ b/Data/Raw/wa_local.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\WA-FEWP\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F78ACF-B2E3-49DF-BD23-9240ECA0928F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC7F19E2-A8AF-4B65-8AF5-C52161EB7E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
   </bookViews>
   <sheets>
     <sheet name="names" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="MPV pursuit data description" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3621" uniqueCount="1470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3635" uniqueCount="1475">
   <si>
     <t>waID</t>
   </si>
@@ -4481,6 +4482,21 @@
   </si>
   <si>
     <t>https://content.govdelivery.com/attachments/WAKING/2026/02/09/file_attachments/3549182/Decedents%20List_02092026.pdf</t>
+  </si>
+  <si>
+    <t>Aaron Ammann</t>
+  </si>
+  <si>
+    <t>The sheriff’s office said law enforcement  responded to a property on Road L.9 Northeast for an open investigation.  While deputies and officers with the Moses Lake Police Department searched the property, they allegedly found Ammann armed with a rifle inside a small barn.  The sheriff’s office said Ammann came out of the barn with the rifle leveled toward law enforcement.  Five deputies fired their weapons, killing him.</t>
+  </si>
+  <si>
+    <t>https://www.kxly.com/news/man-dies-after-being-shot-by-sheriffs-office-deputies-in-rural-moses-lake/article_ec53db6c-b4ce-4fd8-8115-f07eb3951005.html</t>
+  </si>
+  <si>
+    <t>Debbie Novak and Eastern Region may reach out to the man's family</t>
+  </si>
+  <si>
+    <t>4700 Rd L.9 NE</t>
   </si>
 </sst>
 </file>
@@ -4572,7 +4588,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4610,11 +4626,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4928,9 +4939,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}" name="Table2" displayName="Table2" ref="A1:AI230" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A1:AI230" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI230">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}" name="Table2" displayName="Table2" ref="A1:AI231" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A1:AI231" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:AI219">
     <sortCondition ref="A1:A230"/>
   </sortState>
   <tableColumns count="35">
@@ -5272,37 +5283,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A26517-14A9-4E8E-8064-5F228E1B70B4}">
   <dimension ref="A1:AI249"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="7.28515625" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" customWidth="1"/>
+    <col min="4" max="4" width="32.26953125" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" customWidth="1"/>
+    <col min="8" max="8" width="10.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.81640625" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" customWidth="1"/>
-    <col min="16" max="16" width="24.85546875" customWidth="1"/>
-    <col min="17" max="17" width="16.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.1796875" customWidth="1"/>
+    <col min="14" max="14" width="11.7265625" customWidth="1"/>
+    <col min="15" max="15" width="10.453125" customWidth="1"/>
+    <col min="16" max="16" width="24.81640625" customWidth="1"/>
+    <col min="17" max="17" width="16.81640625" customWidth="1"/>
     <col min="18" max="20" width="14" customWidth="1"/>
-    <col min="21" max="21" width="17.5703125" customWidth="1"/>
-    <col min="23" max="23" width="10.28515625" customWidth="1"/>
-    <col min="24" max="24" width="9.42578125" customWidth="1"/>
-    <col min="25" max="25" width="11.42578125" customWidth="1"/>
-    <col min="26" max="26" width="142.85546875" customWidth="1"/>
-    <col min="27" max="27" width="21.28515625" customWidth="1"/>
-    <col min="28" max="28" width="42.85546875" customWidth="1"/>
-    <col min="29" max="29" width="15.5703125" customWidth="1"/>
-    <col min="30" max="30" width="15.85546875" customWidth="1"/>
-    <col min="31" max="31" width="12.42578125" customWidth="1"/>
+    <col min="21" max="21" width="17.54296875" customWidth="1"/>
+    <col min="23" max="23" width="10.26953125" customWidth="1"/>
+    <col min="24" max="24" width="9.453125" customWidth="1"/>
+    <col min="25" max="25" width="11.453125" customWidth="1"/>
+    <col min="26" max="26" width="142.81640625" customWidth="1"/>
+    <col min="27" max="27" width="21.26953125" customWidth="1"/>
+    <col min="28" max="28" width="42.81640625" customWidth="1"/>
+    <col min="29" max="29" width="15.54296875" customWidth="1"/>
+    <col min="30" max="30" width="15.81640625" customWidth="1"/>
+    <col min="31" max="31" width="12.453125" customWidth="1"/>
     <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="34" max="34" width="22.7109375" customWidth="1"/>
-    <col min="35" max="35" width="9.140625" style="13"/>
+    <col min="34" max="34" width="22.7265625" customWidth="1"/>
+    <col min="35" max="35" width="9.1796875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5409,7 +5420,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14">
         <v>90001</v>
       </c>
@@ -5475,7 +5486,7 @@
       </c>
       <c r="AI2" s="16"/>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>90002</v>
       </c>
@@ -5543,7 +5554,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>90003</v>
       </c>
@@ -5614,7 +5625,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>90004</v>
       </c>
@@ -5682,7 +5693,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>90005</v>
       </c>
@@ -5756,7 +5767,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>90006</v>
       </c>
@@ -5824,7 +5835,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>90007</v>
       </c>
@@ -5895,7 +5906,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>90008</v>
       </c>
@@ -5966,7 +5977,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>90009</v>
       </c>
@@ -6037,7 +6048,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>90010</v>
       </c>
@@ -6105,7 +6116,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>90011</v>
       </c>
@@ -6179,7 +6190,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>90012</v>
       </c>
@@ -6256,7 +6267,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>90013</v>
       </c>
@@ -6316,7 +6327,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>90014</v>
       </c>
@@ -6378,7 +6389,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>90015</v>
       </c>
@@ -6446,7 +6457,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>90016</v>
       </c>
@@ -6526,7 +6537,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>90017</v>
       </c>
@@ -6591,7 +6602,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>90018</v>
       </c>
@@ -6659,7 +6670,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>90019</v>
       </c>
@@ -6724,7 +6735,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>90020</v>
       </c>
@@ -6790,7 +6801,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>90021</v>
       </c>
@@ -6861,7 +6872,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>90022</v>
       </c>
@@ -6935,7 +6946,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>90023</v>
       </c>
@@ -7009,7 +7020,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>90024</v>
       </c>
@@ -7086,7 +7097,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>90025</v>
       </c>
@@ -7154,7 +7165,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>90026</v>
       </c>
@@ -7228,7 +7239,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>90027</v>
       </c>
@@ -7290,7 +7301,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>90028</v>
       </c>
@@ -7364,7 +7375,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>90029</v>
       </c>
@@ -7435,7 +7446,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>90030</v>
       </c>
@@ -7512,7 +7523,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>90031</v>
       </c>
@@ -7574,7 +7585,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>90032</v>
       </c>
@@ -7648,7 +7659,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>90033</v>
       </c>
@@ -7719,7 +7730,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>90034</v>
       </c>
@@ -7799,7 +7810,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>90035</v>
       </c>
@@ -7867,7 +7878,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>90036</v>
       </c>
@@ -7932,7 +7943,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="38" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="14">
         <v>90037</v>
       </c>
@@ -7989,7 +8000,7 @@
       </c>
       <c r="AI38" s="16"/>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>90038</v>
       </c>
@@ -8057,7 +8068,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>90039</v>
       </c>
@@ -8128,7 +8139,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>90040</v>
       </c>
@@ -8202,7 +8213,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>90041</v>
       </c>
@@ -8264,7 +8275,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>90042</v>
       </c>
@@ -8329,7 +8340,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>90043</v>
       </c>
@@ -8394,7 +8405,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>90044</v>
       </c>
@@ -8465,7 +8476,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>90045</v>
       </c>
@@ -8539,7 +8550,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>90046</v>
       </c>
@@ -8613,7 +8624,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>90047</v>
       </c>
@@ -8688,7 +8699,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>90048</v>
       </c>
@@ -8757,7 +8768,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>90049</v>
       </c>
@@ -8828,7 +8839,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>90050</v>
       </c>
@@ -8896,7 +8907,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>90051</v>
       </c>
@@ -8970,7 +8981,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>90052</v>
       </c>
@@ -9032,7 +9043,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>90053</v>
       </c>
@@ -9097,7 +9108,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>90054</v>
       </c>
@@ -9168,7 +9179,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>90055</v>
       </c>
@@ -9236,7 +9247,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>90056</v>
       </c>
@@ -9304,7 +9315,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>90057</v>
       </c>
@@ -9381,7 +9392,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="59" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="14">
         <v>90058</v>
       </c>
@@ -9450,7 +9461,7 @@
       </c>
       <c r="AI59" s="16"/>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>90059</v>
       </c>
@@ -9515,7 +9526,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>90060</v>
       </c>
@@ -9586,7 +9597,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>90061</v>
       </c>
@@ -9657,7 +9668,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>90062</v>
       </c>
@@ -9728,7 +9739,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>90063</v>
       </c>
@@ -9799,7 +9810,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>90064</v>
       </c>
@@ -9873,7 +9884,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>90065</v>
       </c>
@@ -9944,7 +9955,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>90066</v>
       </c>
@@ -10010,7 +10021,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>90067</v>
       </c>
@@ -10078,7 +10089,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>90068</v>
       </c>
@@ -10144,7 +10155,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>90069</v>
       </c>
@@ -10215,7 +10226,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>90070</v>
       </c>
@@ -10277,7 +10288,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>90071</v>
       </c>
@@ -10348,7 +10359,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>90072</v>
       </c>
@@ -10419,7 +10430,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>90073</v>
       </c>
@@ -10487,7 +10498,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>90074</v>
       </c>
@@ -10564,7 +10575,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>90075</v>
       </c>
@@ -10635,7 +10646,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>90076</v>
       </c>
@@ -10703,7 +10714,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>90077</v>
       </c>
@@ -10777,7 +10788,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="79" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="14">
         <v>90078</v>
       </c>
@@ -10849,7 +10860,7 @@
       </c>
       <c r="AI79" s="16"/>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>90079</v>
       </c>
@@ -10923,7 +10934,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>90080</v>
       </c>
@@ -10991,7 +11002,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>90081</v>
       </c>
@@ -11059,7 +11070,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>90082</v>
       </c>
@@ -11127,7 +11138,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>90083</v>
       </c>
@@ -11201,7 +11212,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>90084</v>
       </c>
@@ -11272,7 +11283,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>90085</v>
       </c>
@@ -11343,7 +11354,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>90086</v>
       </c>
@@ -11420,7 +11431,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>90087</v>
       </c>
@@ -11488,7 +11499,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>90088</v>
       </c>
@@ -11550,7 +11561,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>90089</v>
       </c>
@@ -11627,7 +11638,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90091</v>
       </c>
@@ -11692,7 +11703,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90092</v>
       </c>
@@ -11763,7 +11774,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>90093</v>
       </c>
@@ -11831,7 +11842,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>90094</v>
       </c>
@@ -11893,7 +11904,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>90095</v>
       </c>
@@ -11964,7 +11975,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>90096</v>
       </c>
@@ -12032,7 +12043,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>90097</v>
       </c>
@@ -12106,7 +12117,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>90098</v>
       </c>
@@ -12174,7 +12185,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>90099</v>
       </c>
@@ -12230,7 +12241,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>90100</v>
       </c>
@@ -12301,7 +12312,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>90101</v>
       </c>
@@ -12372,7 +12383,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>90102</v>
       </c>
@@ -12443,7 +12454,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>90103</v>
       </c>
@@ -12514,7 +12525,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>90104</v>
       </c>
@@ -12579,7 +12590,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>90105</v>
       </c>
@@ -12647,7 +12658,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>90106</v>
       </c>
@@ -12715,7 +12726,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>90107</v>
       </c>
@@ -12789,7 +12800,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>90108</v>
       </c>
@@ -12854,7 +12865,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>90109</v>
       </c>
@@ -12925,7 +12936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>90110</v>
       </c>
@@ -12993,7 +13004,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>90111</v>
       </c>
@@ -13067,7 +13078,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>90112</v>
       </c>
@@ -13132,7 +13143,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>90113</v>
       </c>
@@ -13206,7 +13217,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>90114</v>
       </c>
@@ -13280,7 +13291,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>90115</v>
       </c>
@@ -13360,7 +13371,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>90116</v>
       </c>
@@ -13420,7 +13431,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="117" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>90117</v>
       </c>
@@ -13480,7 +13491,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="118" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>90118</v>
       </c>
@@ -13551,7 +13562,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="119" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>90119</v>
       </c>
@@ -13619,7 +13630,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>90120</v>
       </c>
@@ -13693,7 +13704,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>90121</v>
       </c>
@@ -13764,7 +13775,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>90122</v>
       </c>
@@ -13835,7 +13846,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>90123</v>
       </c>
@@ -13900,7 +13911,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>90124</v>
       </c>
@@ -13968,7 +13979,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>90125</v>
       </c>
@@ -14042,7 +14053,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>90126</v>
       </c>
@@ -14113,7 +14124,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="127" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>90127</v>
       </c>
@@ -14178,7 +14189,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="128" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>90128</v>
       </c>
@@ -14243,7 +14254,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>90129</v>
       </c>
@@ -14323,7 +14334,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>90130</v>
       </c>
@@ -14388,7 +14399,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>90131</v>
       </c>
@@ -14454,7 +14465,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="14">
         <v>90132</v>
       </c>
@@ -14517,7 +14528,7 @@
       </c>
       <c r="AI132" s="16"/>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>90133</v>
       </c>
@@ -14582,7 +14593,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>90135</v>
       </c>
@@ -14653,7 +14664,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>90136</v>
       </c>
@@ -14724,7 +14735,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>90137</v>
       </c>
@@ -14795,7 +14806,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>90138</v>
       </c>
@@ -14866,7 +14877,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>90139</v>
       </c>
@@ -14937,7 +14948,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>90140</v>
       </c>
@@ -15014,7 +15025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>90141</v>
       </c>
@@ -15085,7 +15096,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>90142</v>
       </c>
@@ -15165,7 +15176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A142" s="14">
         <v>90143</v>
       </c>
@@ -15221,7 +15232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>90144</v>
       </c>
@@ -15296,7 +15307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>90145</v>
       </c>
@@ -15356,7 +15367,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="145" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>90146</v>
       </c>
@@ -15439,7 +15450,7 @@
       </c>
       <c r="AI145" s="13"/>
     </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>90147</v>
       </c>
@@ -15505,7 +15516,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>90148</v>
       </c>
@@ -15573,7 +15584,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>90149</v>
       </c>
@@ -15650,7 +15661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A149" s="14">
         <v>90150</v>
       </c>
@@ -15713,7 +15724,7 @@
       </c>
       <c r="AI149" s="16"/>
     </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>90151</v>
       </c>
@@ -15787,7 +15798,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>90152</v>
       </c>
@@ -15867,7 +15878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>90153</v>
       </c>
@@ -15938,7 +15949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A153" s="14">
         <v>90154</v>
       </c>
@@ -16001,7 +16012,7 @@
       </c>
       <c r="AI153" s="16"/>
     </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>90155</v>
       </c>
@@ -16063,7 +16074,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>90156</v>
       </c>
@@ -16131,7 +16142,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>90157</v>
       </c>
@@ -16214,7 +16225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A157" s="14">
         <v>90158</v>
       </c>
@@ -16271,7 +16282,7 @@
       </c>
       <c r="AI157" s="16"/>
     </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>90159</v>
       </c>
@@ -16348,7 +16359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>90160</v>
       </c>
@@ -16419,7 +16430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>90161</v>
       </c>
@@ -16499,7 +16510,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>90162</v>
       </c>
@@ -16570,7 +16581,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="162" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>90163</v>
       </c>
@@ -16641,7 +16652,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="163" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>90164</v>
       </c>
@@ -16709,7 +16720,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="164" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>90165</v>
       </c>
@@ -16783,7 +16794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>90166</v>
       </c>
@@ -16851,7 +16862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>90167</v>
       </c>
@@ -16916,7 +16927,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="167" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>90168</v>
       </c>
@@ -16981,7 +16992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>90169</v>
       </c>
@@ -17052,7 +17063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>90170</v>
       </c>
@@ -17132,7 +17143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>90171</v>
       </c>
@@ -17209,7 +17220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>90172</v>
       </c>
@@ -17280,7 +17291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>90173</v>
       </c>
@@ -17354,7 +17365,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A173" s="14">
         <v>90174</v>
       </c>
@@ -17426,7 +17437,7 @@
       </c>
       <c r="AI173" s="16"/>
     </row>
-    <row r="174" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>90175</v>
       </c>
@@ -17486,7 +17497,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="175" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>90176</v>
       </c>
@@ -17560,7 +17571,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="176" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>90177</v>
       </c>
@@ -17634,7 +17645,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="177" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>90178</v>
       </c>
@@ -17700,7 +17711,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="178" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A178" s="14">
         <v>90181</v>
       </c>
@@ -17775,7 +17786,7 @@
       </c>
       <c r="AI178" s="16"/>
     </row>
-    <row r="179" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>90182</v>
       </c>
@@ -17846,7 +17857,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="180" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A180" s="14">
         <v>90183</v>
       </c>
@@ -17915,7 +17926,7 @@
       </c>
       <c r="AI180" s="16"/>
     </row>
-    <row r="181" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>90184</v>
       </c>
@@ -17980,7 +17991,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="182" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A182" s="14">
         <v>90185</v>
       </c>
@@ -18037,7 +18048,7 @@
       </c>
       <c r="AI182" s="16"/>
     </row>
-    <row r="183" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>90186</v>
       </c>
@@ -18105,7 +18116,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="184" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A184" s="14">
         <v>90187</v>
       </c>
@@ -18168,7 +18179,7 @@
       </c>
       <c r="AI184" s="16"/>
     </row>
-    <row r="185" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A185" s="14">
         <v>90188</v>
       </c>
@@ -18234,7 +18245,7 @@
       </c>
       <c r="AI185" s="16"/>
     </row>
-    <row r="186" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A186" s="14">
         <v>90189</v>
       </c>
@@ -18303,7 +18314,7 @@
       </c>
       <c r="AI186" s="16"/>
     </row>
-    <row r="187" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>90190</v>
       </c>
@@ -18377,7 +18388,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="188" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>90191</v>
       </c>
@@ -18448,7 +18459,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="189" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>90192</v>
       </c>
@@ -18519,7 +18530,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="190" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>90193</v>
       </c>
@@ -18599,7 +18610,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="191" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>90194</v>
       </c>
@@ -18679,7 +18690,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="192" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>90195</v>
       </c>
@@ -18759,7 +18770,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="193" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A193" s="14">
         <v>90196</v>
       </c>
@@ -18819,7 +18830,7 @@
       </c>
       <c r="AI193" s="16"/>
     </row>
-    <row r="194" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>90197</v>
       </c>
@@ -18890,7 +18901,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="195" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>90198</v>
       </c>
@@ -18970,7 +18981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>90199</v>
       </c>
@@ -19039,7 +19050,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="197" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>90200</v>
       </c>
@@ -19116,7 +19127,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="198" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>90201</v>
       </c>
@@ -19187,7 +19198,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="199" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>90202</v>
       </c>
@@ -19258,7 +19269,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="200" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A200" s="14">
         <v>90203</v>
       </c>
@@ -19321,7 +19332,7 @@
       </c>
       <c r="AI200" s="16"/>
     </row>
-    <row r="201" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>90204</v>
       </c>
@@ -19392,7 +19403,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="202" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>90205</v>
       </c>
@@ -19458,7 +19469,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="203" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>90206</v>
       </c>
@@ -19529,7 +19540,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="204" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>90207</v>
       </c>
@@ -19609,7 +19620,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="205" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A205" s="14">
         <v>90208</v>
       </c>
@@ -19672,7 +19683,7 @@
       </c>
       <c r="AI205" s="16"/>
     </row>
-    <row r="206" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>90209</v>
       </c>
@@ -19743,7 +19754,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="207" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A207" s="14">
         <v>90210</v>
       </c>
@@ -19815,7 +19826,7 @@
       </c>
       <c r="AI207" s="16"/>
     </row>
-    <row r="208" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A208" s="14">
         <v>90211</v>
       </c>
@@ -19872,7 +19883,7 @@
       </c>
       <c r="AI208" s="16"/>
     </row>
-    <row r="209" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>90212</v>
       </c>
@@ -19949,7 +19960,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="210" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A210" s="14">
         <v>90213</v>
       </c>
@@ -20012,7 +20023,7 @@
       </c>
       <c r="AI210" s="16"/>
     </row>
-    <row r="211" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>90214</v>
       </c>
@@ -20083,7 +20094,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="212" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A212" s="14">
         <v>90215</v>
       </c>
@@ -20152,7 +20163,7 @@
       </c>
       <c r="AI212" s="16"/>
     </row>
-    <row r="213" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>90216</v>
       </c>
@@ -20220,7 +20231,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="214" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>90217</v>
       </c>
@@ -20286,7 +20297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>90218</v>
       </c>
@@ -20352,7 +20363,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="216" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>90219</v>
       </c>
@@ -20424,7 +20435,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="217" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A217" s="14">
         <v>90220</v>
       </c>
@@ -20481,7 +20492,7 @@
       </c>
       <c r="AI217" s="16"/>
     </row>
-    <row r="218" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>90221</v>
       </c>
@@ -20538,7 +20549,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="219" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>90222</v>
       </c>
@@ -20607,7 +20618,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="220" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>90223</v>
       </c>
@@ -20670,7 +20681,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="221" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>90224</v>
       </c>
@@ -20739,7 +20750,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="222" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>90225</v>
       </c>
@@ -20798,7 +20809,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="223" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>90226</v>
       </c>
@@ -20872,7 +20883,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="224" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>90227</v>
       </c>
@@ -20944,7 +20955,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="225" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>90228</v>
       </c>
@@ -21024,7 +21035,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="226" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>90229</v>
       </c>
@@ -21098,7 +21109,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="227" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>90230</v>
       </c>
@@ -21166,7 +21177,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="228" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>90231</v>
       </c>
@@ -21240,223 +21251,260 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="229" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>90232</v>
       </c>
-      <c r="B229" s="20">
+      <c r="B229">
         <v>20639</v>
       </c>
-      <c r="C229" s="20"/>
-      <c r="D229" s="20" t="s">
+      <c r="D229" t="s">
         <v>1459</v>
       </c>
-      <c r="E229" s="21">
+      <c r="E229" s="11">
         <v>46059</v>
       </c>
-      <c r="F229" s="20">
+      <c r="F229">
         <v>57</v>
       </c>
-      <c r="G229" s="20" t="s">
+      <c r="G229" t="s">
         <v>158</v>
       </c>
-      <c r="H229" s="20" t="s">
+      <c r="H229" t="s">
         <v>77</v>
       </c>
-      <c r="I229" s="20" t="s">
+      <c r="I229" t="s">
         <v>1460</v>
       </c>
-      <c r="J229" s="20" t="s">
+      <c r="J229" t="s">
         <v>198</v>
       </c>
-      <c r="K229" s="20">
+      <c r="K229">
         <v>99301</v>
       </c>
-      <c r="L229" s="20" t="s">
+      <c r="L229" t="s">
         <v>199</v>
       </c>
-      <c r="M229" s="20">
+      <c r="M229">
         <v>46.269905700000002</v>
       </c>
-      <c r="N229" s="20">
+      <c r="N229">
         <v>-119.2355493</v>
       </c>
-      <c r="O229" s="20" t="s">
+      <c r="O229" t="s">
         <v>200</v>
       </c>
-      <c r="P229" s="20" t="s">
+      <c r="P229" t="s">
         <v>126</v>
       </c>
-      <c r="Q229" s="20" t="s">
+      <c r="Q229" t="s">
         <v>127</v>
       </c>
-      <c r="R229" s="20" t="s">
+      <c r="R229" t="s">
         <v>147</v>
       </c>
-      <c r="S229" s="20" t="s">
+      <c r="S229" t="s">
         <v>1286</v>
       </c>
-      <c r="T229" s="20"/>
-      <c r="U229" s="20"/>
-      <c r="V229" s="20"/>
-      <c r="W229" s="20"/>
-      <c r="X229" s="20" t="s">
+      <c r="X229" t="s">
         <v>126</v>
       </c>
-      <c r="Y229" s="20"/>
-      <c r="Z229" s="20" t="s">
+      <c r="Z229" t="s">
         <v>1461</v>
       </c>
-      <c r="AA229" s="20" t="s">
+      <c r="AA229" t="s">
         <v>1463</v>
       </c>
-      <c r="AB229" s="20"/>
       <c r="AC229" s="18" t="s">
         <v>1462</v>
       </c>
-      <c r="AD229" s="20"/>
-      <c r="AE229" s="20"/>
-      <c r="AF229" s="20"/>
-      <c r="AG229" s="20"/>
-      <c r="AH229" s="20"/>
-      <c r="AI229" s="22"/>
-    </row>
-    <row r="230" spans="1:35" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>90233</v>
       </c>
-      <c r="B230" s="20">
+      <c r="B230">
         <v>20626</v>
       </c>
-      <c r="C230" s="20"/>
-      <c r="D230" s="20" t="s">
+      <c r="D230" t="s">
         <v>1467</v>
       </c>
-      <c r="E230" s="21">
+      <c r="E230" s="11">
         <v>46059</v>
       </c>
-      <c r="F230" s="20">
+      <c r="F230">
         <v>37</v>
       </c>
-      <c r="G230" s="20" t="s">
+      <c r="G230" t="s">
         <v>30</v>
       </c>
-      <c r="H230" s="20" t="s">
+      <c r="H230" t="s">
         <v>278</v>
       </c>
-      <c r="I230" s="20" t="s">
+      <c r="I230" t="s">
         <v>1464</v>
       </c>
-      <c r="J230" s="20" t="s">
+      <c r="J230" t="s">
         <v>686</v>
       </c>
-      <c r="K230" s="20">
+      <c r="K230">
         <v>98003</v>
       </c>
-      <c r="L230" s="20" t="s">
+      <c r="L230" t="s">
         <v>687</v>
       </c>
-      <c r="M230" s="20">
+      <c r="M230">
         <v>47.3067487</v>
       </c>
-      <c r="N230" s="20">
+      <c r="N230">
         <v>-122.3367776</v>
       </c>
-      <c r="O230" s="20" t="s">
+      <c r="O230" t="s">
         <v>688</v>
       </c>
-      <c r="P230" s="20" t="s">
+      <c r="P230" t="s">
         <v>36</v>
       </c>
-      <c r="Q230" s="20" t="s">
+      <c r="Q230" t="s">
         <v>37</v>
       </c>
-      <c r="R230" s="20"/>
-      <c r="S230" s="20"/>
-      <c r="T230" s="20"/>
-      <c r="U230" s="20"/>
-      <c r="V230" s="20" t="s">
+      <c r="V230" t="s">
         <v>38</v>
       </c>
-      <c r="W230" s="20" t="s">
+      <c r="W230" t="s">
         <v>39</v>
       </c>
-      <c r="X230" s="20" t="s">
+      <c r="X230" t="s">
         <v>54</v>
       </c>
-      <c r="Y230" s="20"/>
-      <c r="Z230" s="20" t="s">
+      <c r="Z230" t="s">
         <v>1465</v>
       </c>
-      <c r="AA230" s="20" t="s">
+      <c r="AA230" t="s">
         <v>1466</v>
       </c>
-      <c r="AB230" s="20"/>
-      <c r="AC230" s="20"/>
-      <c r="AD230" s="20"/>
-      <c r="AE230" s="20"/>
-      <c r="AF230" s="20"/>
-      <c r="AG230" s="20"/>
       <c r="AH230" s="18" t="s">
         <v>1469</v>
       </c>
-      <c r="AI230" s="22"/>
-    </row>
-    <row r="231" spans="1:35" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>90234</v>
+      </c>
+      <c r="B231">
+        <v>20999</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E231" s="11">
+        <v>46069</v>
+      </c>
+      <c r="F231">
+        <v>33</v>
+      </c>
+      <c r="G231" t="s">
+        <v>30</v>
+      </c>
       <c r="H231"/>
-    </row>
-    <row r="232" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="I231" t="s">
+        <v>1474</v>
+      </c>
+      <c r="J231" t="s">
+        <v>487</v>
+      </c>
+      <c r="K231">
+        <v>98837</v>
+      </c>
+      <c r="L231" t="s">
+        <v>488</v>
+      </c>
+      <c r="M231">
+        <v>47.158163199999997</v>
+      </c>
+      <c r="N231">
+        <v>-119.2196026</v>
+      </c>
+      <c r="O231" t="s">
+        <v>489</v>
+      </c>
+      <c r="P231" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>37</v>
+      </c>
+      <c r="V231" t="s">
+        <v>38</v>
+      </c>
+      <c r="W231" t="s">
+        <v>39</v>
+      </c>
+      <c r="X231" t="s">
+        <v>1338</v>
+      </c>
+      <c r="Z231" t="s">
+        <v>1471</v>
+      </c>
+      <c r="AA231" s="18" t="s">
+        <v>1472</v>
+      </c>
+      <c r="AB231" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="232" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H232"/>
     </row>
-    <row r="233" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H233"/>
     </row>
-    <row r="234" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H234"/>
     </row>
-    <row r="235" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H235"/>
     </row>
-    <row r="236" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H236"/>
     </row>
-    <row r="237" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H237"/>
     </row>
-    <row r="238" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H238"/>
     </row>
-    <row r="239" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H239"/>
     </row>
-    <row r="240" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H240"/>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H241"/>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H242"/>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H243"/>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H244"/>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H245"/>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H246"/>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H247"/>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H248"/>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H249"/>
     </row>
   </sheetData>
@@ -21475,11 +21523,12 @@
     <hyperlink ref="AA228" r:id="rId12" xr:uid="{B1EC3581-4906-4044-A05B-2D259FBA0E7E}"/>
     <hyperlink ref="AC229" r:id="rId13" xr:uid="{01A2C460-5A5B-400A-98AC-2BF42B651DEC}"/>
     <hyperlink ref="AH230" r:id="rId14" xr:uid="{771FF646-43C9-4E59-85CA-18A328886EF9}"/>
+    <hyperlink ref="AA231" r:id="rId15" xr:uid="{F3EA0D7B-FAA2-4DBC-B83D-3E20358359D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId15"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
   <tableParts count="1">
-    <tablePart r:id="rId16"/>
+    <tablePart r:id="rId17"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21487,13 +21536,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC9006-39A6-404C-9CCE-6016C38CE417}">
   <dimension ref="A2:Q2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1294</v>
       </c>
@@ -21552,13 +21601,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82750EAF-E5A3-44AA-9CE9-95763C1F48C5}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" customWidth="1"/>
+    <col min="1" max="1" width="26.81640625" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1264</v>
       </c>
@@ -21569,7 +21618,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1267</v>
       </c>
@@ -21580,7 +21629,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1269</v>
       </c>
@@ -21591,7 +21640,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1272</v>
       </c>
@@ -21602,7 +21651,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1274</v>
       </c>
@@ -21613,7 +21662,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1276</v>
       </c>
@@ -21624,7 +21673,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>1278</v>
       </c>
@@ -21635,7 +21684,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>1280</v>
       </c>
@@ -21646,7 +21695,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>1317</v>
       </c>
@@ -21668,68 +21717,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04CD9421-3D04-4EA0-825D-6A17750FBC1A}">
   <dimension ref="B4:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>1329</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B7" s="7" t="s">
         <v>1319</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="C9" s="9" t="s">
         <v>1320</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="C10" s="9" t="s">
         <v>1321</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="C11" s="9" t="s">
         <v>1322</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="C12" s="9" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="C13" s="9" t="s">
         <v>1324</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="C14" s="9"/>
     </row>
-    <row r="15" spans="2:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B15" s="7" t="s">
         <v>1325</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B16" s="8"/>
     </row>
-    <row r="17" spans="3:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="C17" s="9" t="s">
         <v>1326</v>
       </c>
     </row>
-    <row r="18" spans="3:3" ht="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:3" ht="16.5" x14ac:dyDescent="0.35">
       <c r="C18" s="9" t="s">
         <v>1327</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C19" s="10" t="s">
         <v>1328</v>
       </c>

--- a/Data/Raw/wa_local.xlsx
+++ b/Data/Raw/wa_local.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\WA-FEWP\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC7F19E2-A8AF-4B65-8AF5-C52161EB7E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E2D2E8-B532-486E-A743-C2A93D2EBEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
   </bookViews>
   <sheets>
     <sheet name="names" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="MPV pursuit data description" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3635" uniqueCount="1475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3680" uniqueCount="1492">
   <si>
     <t>waID</t>
   </si>
@@ -4497,6 +4496,57 @@
   </si>
   <si>
     <t>4700 Rd L.9 NE</t>
+  </si>
+  <si>
+    <t>Aleksandr Shablykin</t>
+  </si>
+  <si>
+    <t>Gig Harbor</t>
+  </si>
+  <si>
+    <t>The sheriff's office received a call for a no contact order violation, but delayed responding because they realized the order had not yet been served by the Tacoma Police Department.  The order had been approved by a judge almost 10 months earlier.  During the delay, the subject stabbed and killed 4 people, including his mother, who had been granted the no contact order against her son, and 3 neighbors who tried to help.  When the deputy finally arrived, 50 minutes later, he shot and killed the subject.</t>
+  </si>
+  <si>
+    <t>https://www.thenewstribune.com/news/local/article314843054.html</t>
+  </si>
+  <si>
+    <t>https://www.thenewstribune.com/news/local/crime/article314823270.html</t>
+  </si>
+  <si>
+    <t>https://www.piercecountywa.gov/6996/Media-Release-Information</t>
+  </si>
+  <si>
+    <t>https://www.piercecountywa.gov/DocumentCenter/View/155207/PCFIT-Pierce-County-January-30-2026</t>
+  </si>
+  <si>
+    <t>https://www.spokesman.com/stories/2026/feb/25/police-shoot-kill-suspect-in-apple-tree-inn-homici/</t>
+  </si>
+  <si>
+    <t>Richard Sheppard</t>
+  </si>
+  <si>
+    <t>1800 West Carlisle Avenue</t>
+  </si>
+  <si>
+    <t>Spokane PD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Police shot and killed a man who they allege was a suspect in an earlier homicide at a north Spokane motel.  He was allegedly fleeing through neighborhood yards, armed with a long gun. </t>
+  </si>
+  <si>
+    <t>14000 87th Avenue Court NW</t>
+  </si>
+  <si>
+    <t>1600 North Pines Road</t>
+  </si>
+  <si>
+    <t>Spokane Valley Police Department</t>
+  </si>
+  <si>
+    <t>Spokane County deputies responded to 911 call saying a blue Dodge truck was crashing into cars and later into a mailbox.   Police arrived and reported seeing the driver holding a gun to his head. According to the sheriff’s office, deputies were able to de-escalate the situation and the driver placed the gun on the ground, but then he suddenly picked the gun back up, fled to the front of his truck and shot himself.</t>
+  </si>
+  <si>
+    <t>https://www.spokesman.com/stories/2026/feb/23/spokane-valley-hit-and-run-ends-in-suicide/</t>
   </si>
 </sst>
 </file>
@@ -4588,7 +4638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4626,6 +4676,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4939,8 +4994,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}" name="Table2" displayName="Table2" ref="A1:AI231" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A1:AI231" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}" name="Table2" displayName="Table2" ref="A1:AI234" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A1:AI234" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:AI219">
     <sortCondition ref="A1:A230"/>
   </sortState>
@@ -5283,37 +5338,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A26517-14A9-4E8E-8064-5F228E1B70B4}">
   <dimension ref="A1:AI249"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="7.26953125" customWidth="1"/>
-    <col min="4" max="4" width="32.26953125" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1"/>
-    <col min="8" max="8" width="10.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.1796875" customWidth="1"/>
-    <col min="14" max="14" width="11.7265625" customWidth="1"/>
-    <col min="15" max="15" width="10.453125" customWidth="1"/>
-    <col min="16" max="16" width="24.81640625" customWidth="1"/>
-    <col min="17" max="17" width="16.81640625" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="24.85546875" customWidth="1"/>
+    <col min="17" max="17" width="16.85546875" customWidth="1"/>
     <col min="18" max="20" width="14" customWidth="1"/>
-    <col min="21" max="21" width="17.54296875" customWidth="1"/>
-    <col min="23" max="23" width="10.26953125" customWidth="1"/>
-    <col min="24" max="24" width="9.453125" customWidth="1"/>
-    <col min="25" max="25" width="11.453125" customWidth="1"/>
-    <col min="26" max="26" width="142.81640625" customWidth="1"/>
-    <col min="27" max="27" width="21.26953125" customWidth="1"/>
-    <col min="28" max="28" width="42.81640625" customWidth="1"/>
-    <col min="29" max="29" width="15.54296875" customWidth="1"/>
-    <col min="30" max="30" width="15.81640625" customWidth="1"/>
-    <col min="31" max="31" width="12.453125" customWidth="1"/>
+    <col min="21" max="21" width="17.5703125" customWidth="1"/>
+    <col min="23" max="23" width="10.28515625" customWidth="1"/>
+    <col min="24" max="24" width="9.42578125" customWidth="1"/>
+    <col min="25" max="25" width="11.42578125" customWidth="1"/>
+    <col min="26" max="26" width="142.85546875" customWidth="1"/>
+    <col min="27" max="27" width="21.28515625" customWidth="1"/>
+    <col min="28" max="28" width="42.85546875" customWidth="1"/>
+    <col min="29" max="29" width="15.5703125" customWidth="1"/>
+    <col min="30" max="30" width="15.85546875" customWidth="1"/>
+    <col min="31" max="31" width="12.42578125" customWidth="1"/>
     <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="34" max="34" width="22.7265625" customWidth="1"/>
-    <col min="35" max="35" width="9.1796875" style="13"/>
+    <col min="34" max="34" width="22.7109375" customWidth="1"/>
+    <col min="35" max="35" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5420,7 +5475,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>90001</v>
       </c>
@@ -5486,7 +5541,7 @@
       </c>
       <c r="AI2" s="16"/>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>90002</v>
       </c>
@@ -5554,7 +5609,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>90003</v>
       </c>
@@ -5625,7 +5680,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>90004</v>
       </c>
@@ -5693,7 +5748,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>90005</v>
       </c>
@@ -5767,7 +5822,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>90006</v>
       </c>
@@ -5835,7 +5890,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>90007</v>
       </c>
@@ -5906,7 +5961,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>90008</v>
       </c>
@@ -5977,7 +6032,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>90009</v>
       </c>
@@ -6048,7 +6103,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>90010</v>
       </c>
@@ -6116,7 +6171,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>90011</v>
       </c>
@@ -6190,7 +6245,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>90012</v>
       </c>
@@ -6267,7 +6322,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>90013</v>
       </c>
@@ -6327,7 +6382,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>90014</v>
       </c>
@@ -6389,7 +6444,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>90015</v>
       </c>
@@ -6457,7 +6512,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>90016</v>
       </c>
@@ -6537,7 +6592,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>90017</v>
       </c>
@@ -6602,7 +6657,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>90018</v>
       </c>
@@ -6670,7 +6725,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>90019</v>
       </c>
@@ -6735,7 +6790,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>90020</v>
       </c>
@@ -6801,7 +6856,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>90021</v>
       </c>
@@ -6872,7 +6927,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>90022</v>
       </c>
@@ -6946,7 +7001,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>90023</v>
       </c>
@@ -7020,7 +7075,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>90024</v>
       </c>
@@ -7097,7 +7152,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>90025</v>
       </c>
@@ -7165,7 +7220,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>90026</v>
       </c>
@@ -7239,7 +7294,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>90027</v>
       </c>
@@ -7301,7 +7356,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>90028</v>
       </c>
@@ -7375,7 +7430,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>90029</v>
       </c>
@@ -7446,7 +7501,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>90030</v>
       </c>
@@ -7523,7 +7578,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>90031</v>
       </c>
@@ -7585,7 +7640,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>90032</v>
       </c>
@@ -7659,7 +7714,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>90033</v>
       </c>
@@ -7730,7 +7785,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>90034</v>
       </c>
@@ -7810,7 +7865,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>90035</v>
       </c>
@@ -7878,7 +7933,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>90036</v>
       </c>
@@ -7943,7 +7998,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="38" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>90037</v>
       </c>
@@ -8000,7 +8055,7 @@
       </c>
       <c r="AI38" s="16"/>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>90038</v>
       </c>
@@ -8068,7 +8123,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>90039</v>
       </c>
@@ -8139,7 +8194,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>90040</v>
       </c>
@@ -8213,7 +8268,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>90041</v>
       </c>
@@ -8275,7 +8330,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>90042</v>
       </c>
@@ -8340,7 +8395,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>90043</v>
       </c>
@@ -8405,7 +8460,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>90044</v>
       </c>
@@ -8476,7 +8531,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>90045</v>
       </c>
@@ -8550,7 +8605,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>90046</v>
       </c>
@@ -8624,7 +8679,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>90047</v>
       </c>
@@ -8699,7 +8754,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>90048</v>
       </c>
@@ -8768,7 +8823,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>90049</v>
       </c>
@@ -8839,7 +8894,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>90050</v>
       </c>
@@ -8907,7 +8962,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>90051</v>
       </c>
@@ -8981,7 +9036,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>90052</v>
       </c>
@@ -9043,7 +9098,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>90053</v>
       </c>
@@ -9108,7 +9163,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>90054</v>
       </c>
@@ -9179,7 +9234,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>90055</v>
       </c>
@@ -9247,7 +9302,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>90056</v>
       </c>
@@ -9315,7 +9370,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>90057</v>
       </c>
@@ -9392,7 +9447,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="59" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>90058</v>
       </c>
@@ -9461,7 +9516,7 @@
       </c>
       <c r="AI59" s="16"/>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>90059</v>
       </c>
@@ -9526,7 +9581,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>90060</v>
       </c>
@@ -9597,7 +9652,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>90061</v>
       </c>
@@ -9668,7 +9723,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>90062</v>
       </c>
@@ -9739,7 +9794,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>90063</v>
       </c>
@@ -9810,7 +9865,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>90064</v>
       </c>
@@ -9884,7 +9939,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>90065</v>
       </c>
@@ -9955,7 +10010,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>90066</v>
       </c>
@@ -10021,7 +10076,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>90067</v>
       </c>
@@ -10089,7 +10144,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>90068</v>
       </c>
@@ -10155,7 +10210,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>90069</v>
       </c>
@@ -10226,7 +10281,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>90070</v>
       </c>
@@ -10288,7 +10343,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>90071</v>
       </c>
@@ -10359,7 +10414,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>90072</v>
       </c>
@@ -10430,7 +10485,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>90073</v>
       </c>
@@ -10498,7 +10553,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>90074</v>
       </c>
@@ -10575,7 +10630,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>90075</v>
       </c>
@@ -10646,7 +10701,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>90076</v>
       </c>
@@ -10714,7 +10769,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>90077</v>
       </c>
@@ -10788,7 +10843,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="79" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="14">
         <v>90078</v>
       </c>
@@ -10860,7 +10915,7 @@
       </c>
       <c r="AI79" s="16"/>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>90079</v>
       </c>
@@ -10934,7 +10989,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>90080</v>
       </c>
@@ -11002,7 +11057,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>90081</v>
       </c>
@@ -11070,7 +11125,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>90082</v>
       </c>
@@ -11138,7 +11193,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>90083</v>
       </c>
@@ -11212,7 +11267,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>90084</v>
       </c>
@@ -11283,7 +11338,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>90085</v>
       </c>
@@ -11354,7 +11409,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>90086</v>
       </c>
@@ -11431,7 +11486,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>90087</v>
       </c>
@@ -11499,7 +11554,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>90088</v>
       </c>
@@ -11561,7 +11616,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>90089</v>
       </c>
@@ -11638,7 +11693,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90091</v>
       </c>
@@ -11703,7 +11758,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>90092</v>
       </c>
@@ -11774,7 +11829,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>90093</v>
       </c>
@@ -11842,7 +11897,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90094</v>
       </c>
@@ -11904,7 +11959,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>90095</v>
       </c>
@@ -11975,7 +12030,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>90096</v>
       </c>
@@ -12043,7 +12098,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>90097</v>
       </c>
@@ -12117,7 +12172,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>90098</v>
       </c>
@@ -12185,7 +12240,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>90099</v>
       </c>
@@ -12241,7 +12296,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>90100</v>
       </c>
@@ -12312,7 +12367,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>90101</v>
       </c>
@@ -12383,7 +12438,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>90102</v>
       </c>
@@ -12454,7 +12509,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>90103</v>
       </c>
@@ -12525,7 +12580,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>90104</v>
       </c>
@@ -12590,7 +12645,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>90105</v>
       </c>
@@ -12658,7 +12713,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>90106</v>
       </c>
@@ -12726,7 +12781,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>90107</v>
       </c>
@@ -12800,7 +12855,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>90108</v>
       </c>
@@ -12865,7 +12920,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>90109</v>
       </c>
@@ -12936,7 +12991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>90110</v>
       </c>
@@ -13004,7 +13059,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>90111</v>
       </c>
@@ -13078,7 +13133,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>90112</v>
       </c>
@@ -13143,7 +13198,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>90113</v>
       </c>
@@ -13217,7 +13272,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>90114</v>
       </c>
@@ -13291,7 +13346,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>90115</v>
       </c>
@@ -13371,7 +13426,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>90116</v>
       </c>
@@ -13431,7 +13486,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="117" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>90117</v>
       </c>
@@ -13491,7 +13546,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="118" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>90118</v>
       </c>
@@ -13562,7 +13617,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="119" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>90119</v>
       </c>
@@ -13630,7 +13685,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>90120</v>
       </c>
@@ -13704,7 +13759,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>90121</v>
       </c>
@@ -13775,7 +13830,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>90122</v>
       </c>
@@ -13846,7 +13901,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>90123</v>
       </c>
@@ -13911,7 +13966,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>90124</v>
       </c>
@@ -13979,7 +14034,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>90125</v>
       </c>
@@ -14053,7 +14108,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>90126</v>
       </c>
@@ -14124,7 +14179,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="127" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>90127</v>
       </c>
@@ -14189,7 +14244,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="128" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>90128</v>
       </c>
@@ -14254,7 +14309,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>90129</v>
       </c>
@@ -14334,7 +14389,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>90130</v>
       </c>
@@ -14399,7 +14454,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>90131</v>
       </c>
@@ -14465,7 +14520,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="14">
         <v>90132</v>
       </c>
@@ -14528,7 +14583,7 @@
       </c>
       <c r="AI132" s="16"/>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>90133</v>
       </c>
@@ -14593,7 +14648,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>90135</v>
       </c>
@@ -14664,7 +14719,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>90136</v>
       </c>
@@ -14735,7 +14790,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>90137</v>
       </c>
@@ -14806,7 +14861,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>90138</v>
       </c>
@@ -14877,7 +14932,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>90139</v>
       </c>
@@ -14948,7 +15003,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>90140</v>
       </c>
@@ -15025,7 +15080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>90141</v>
       </c>
@@ -15096,7 +15151,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>90142</v>
       </c>
@@ -15176,7 +15231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="14">
         <v>90143</v>
       </c>
@@ -15232,7 +15287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>90144</v>
       </c>
@@ -15307,7 +15362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>90145</v>
       </c>
@@ -15367,7 +15422,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="145" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>90146</v>
       </c>
@@ -15450,7 +15505,7 @@
       </c>
       <c r="AI145" s="13"/>
     </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>90147</v>
       </c>
@@ -15516,7 +15571,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>90148</v>
       </c>
@@ -15584,7 +15639,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>90149</v>
       </c>
@@ -15661,7 +15716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="14">
         <v>90150</v>
       </c>
@@ -15724,7 +15779,7 @@
       </c>
       <c r="AI149" s="16"/>
     </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>90151</v>
       </c>
@@ -15798,7 +15853,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>90152</v>
       </c>
@@ -15878,7 +15933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>90153</v>
       </c>
@@ -15949,7 +16004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="14">
         <v>90154</v>
       </c>
@@ -16012,7 +16067,7 @@
       </c>
       <c r="AI153" s="16"/>
     </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>90155</v>
       </c>
@@ -16074,7 +16129,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>90156</v>
       </c>
@@ -16142,7 +16197,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>90157</v>
       </c>
@@ -16225,7 +16280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="14">
         <v>90158</v>
       </c>
@@ -16282,7 +16337,7 @@
       </c>
       <c r="AI157" s="16"/>
     </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>90159</v>
       </c>
@@ -16359,7 +16414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>90160</v>
       </c>
@@ -16430,7 +16485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>90161</v>
       </c>
@@ -16510,7 +16565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>90162</v>
       </c>
@@ -16581,7 +16636,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="162" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>90163</v>
       </c>
@@ -16652,7 +16707,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="163" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>90164</v>
       </c>
@@ -16720,7 +16775,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="164" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>90165</v>
       </c>
@@ -16794,7 +16849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>90166</v>
       </c>
@@ -16862,7 +16917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>90167</v>
       </c>
@@ -16927,7 +16982,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="167" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>90168</v>
       </c>
@@ -16992,7 +17047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>90169</v>
       </c>
@@ -17063,7 +17118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>90170</v>
       </c>
@@ -17143,7 +17198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>90171</v>
       </c>
@@ -17220,7 +17275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>90172</v>
       </c>
@@ -17291,7 +17346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>90173</v>
       </c>
@@ -17365,7 +17420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="14">
         <v>90174</v>
       </c>
@@ -17437,7 +17492,7 @@
       </c>
       <c r="AI173" s="16"/>
     </row>
-    <row r="174" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>90175</v>
       </c>
@@ -17497,7 +17552,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="175" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>90176</v>
       </c>
@@ -17571,7 +17626,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="176" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>90177</v>
       </c>
@@ -17645,7 +17700,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="177" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>90178</v>
       </c>
@@ -17711,7 +17766,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="178" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="14">
         <v>90181</v>
       </c>
@@ -17786,7 +17841,7 @@
       </c>
       <c r="AI178" s="16"/>
     </row>
-    <row r="179" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>90182</v>
       </c>
@@ -17857,7 +17912,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="180" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="14">
         <v>90183</v>
       </c>
@@ -17926,7 +17981,7 @@
       </c>
       <c r="AI180" s="16"/>
     </row>
-    <row r="181" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>90184</v>
       </c>
@@ -17991,7 +18046,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="182" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="14">
         <v>90185</v>
       </c>
@@ -18048,7 +18103,7 @@
       </c>
       <c r="AI182" s="16"/>
     </row>
-    <row r="183" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>90186</v>
       </c>
@@ -18116,7 +18171,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="184" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="14">
         <v>90187</v>
       </c>
@@ -18179,7 +18234,7 @@
       </c>
       <c r="AI184" s="16"/>
     </row>
-    <row r="185" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="14">
         <v>90188</v>
       </c>
@@ -18245,7 +18300,7 @@
       </c>
       <c r="AI185" s="16"/>
     </row>
-    <row r="186" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="14">
         <v>90189</v>
       </c>
@@ -18314,7 +18369,7 @@
       </c>
       <c r="AI186" s="16"/>
     </row>
-    <row r="187" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>90190</v>
       </c>
@@ -18388,7 +18443,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="188" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>90191</v>
       </c>
@@ -18459,7 +18514,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="189" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>90192</v>
       </c>
@@ -18530,7 +18585,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="190" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>90193</v>
       </c>
@@ -18610,7 +18665,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="191" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>90194</v>
       </c>
@@ -18690,7 +18745,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="192" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>90195</v>
       </c>
@@ -18770,7 +18825,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="193" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="14">
         <v>90196</v>
       </c>
@@ -18830,7 +18885,7 @@
       </c>
       <c r="AI193" s="16"/>
     </row>
-    <row r="194" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>90197</v>
       </c>
@@ -18901,7 +18956,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="195" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>90198</v>
       </c>
@@ -18981,7 +19036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>90199</v>
       </c>
@@ -19050,7 +19105,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="197" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>90200</v>
       </c>
@@ -19127,7 +19182,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="198" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>90201</v>
       </c>
@@ -19198,7 +19253,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="199" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>90202</v>
       </c>
@@ -19269,7 +19324,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="200" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="14">
         <v>90203</v>
       </c>
@@ -19332,7 +19387,7 @@
       </c>
       <c r="AI200" s="16"/>
     </row>
-    <row r="201" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>90204</v>
       </c>
@@ -19403,7 +19458,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="202" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>90205</v>
       </c>
@@ -19469,7 +19524,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="203" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>90206</v>
       </c>
@@ -19540,7 +19595,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="204" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>90207</v>
       </c>
@@ -19620,7 +19675,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="205" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="14">
         <v>90208</v>
       </c>
@@ -19683,7 +19738,7 @@
       </c>
       <c r="AI205" s="16"/>
     </row>
-    <row r="206" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>90209</v>
       </c>
@@ -19754,7 +19809,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="207" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="14">
         <v>90210</v>
       </c>
@@ -19826,7 +19881,7 @@
       </c>
       <c r="AI207" s="16"/>
     </row>
-    <row r="208" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="14">
         <v>90211</v>
       </c>
@@ -19883,7 +19938,7 @@
       </c>
       <c r="AI208" s="16"/>
     </row>
-    <row r="209" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>90212</v>
       </c>
@@ -19960,7 +20015,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="210" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="14">
         <v>90213</v>
       </c>
@@ -20023,7 +20078,7 @@
       </c>
       <c r="AI210" s="16"/>
     </row>
-    <row r="211" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>90214</v>
       </c>
@@ -20094,7 +20149,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="212" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="14">
         <v>90215</v>
       </c>
@@ -20163,7 +20218,7 @@
       </c>
       <c r="AI212" s="16"/>
     </row>
-    <row r="213" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>90216</v>
       </c>
@@ -20231,7 +20286,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="214" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>90217</v>
       </c>
@@ -20297,7 +20352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>90218</v>
       </c>
@@ -20363,7 +20418,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="216" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>90219</v>
       </c>
@@ -20435,7 +20490,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="217" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="14">
         <v>90220</v>
       </c>
@@ -20492,7 +20547,7 @@
       </c>
       <c r="AI217" s="16"/>
     </row>
-    <row r="218" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>90221</v>
       </c>
@@ -20549,7 +20604,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="219" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>90222</v>
       </c>
@@ -20618,7 +20673,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="220" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>90223</v>
       </c>
@@ -20681,7 +20736,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="221" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>90224</v>
       </c>
@@ -20750,7 +20805,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="222" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>90225</v>
       </c>
@@ -20809,7 +20864,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="223" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>90226</v>
       </c>
@@ -20883,7 +20938,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="224" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>90227</v>
       </c>
@@ -20955,7 +21010,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="225" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>90228</v>
       </c>
@@ -21035,7 +21090,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="226" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>90229</v>
       </c>
@@ -21109,7 +21164,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="227" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>90230</v>
       </c>
@@ -21176,8 +21231,14 @@
       <c r="AC227" s="12" t="s">
         <v>1444</v>
       </c>
-    </row>
-    <row r="228" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="AG227" t="s">
+        <v>1481</v>
+      </c>
+      <c r="AH227" s="20" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="228" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>90231</v>
       </c>
@@ -21251,7 +21312,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="229" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>90232</v>
       </c>
@@ -21319,7 +21380,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="230" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>90233</v>
       </c>
@@ -21387,7 +21448,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="231" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>90234</v>
       </c>
@@ -21453,58 +21514,290 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="232" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="H232"/>
-    </row>
-    <row r="233" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="H233"/>
-    </row>
-    <row r="234" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="H234"/>
-    </row>
-    <row r="235" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A232" s="20">
+        <v>90235</v>
+      </c>
+      <c r="B232" s="20">
+        <v>21274</v>
+      </c>
+      <c r="C232" s="20"/>
+      <c r="D232" s="20" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E232" s="21">
+        <v>46077</v>
+      </c>
+      <c r="F232" s="20">
+        <v>32</v>
+      </c>
+      <c r="G232" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H232" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I232" s="20" t="s">
+        <v>1487</v>
+      </c>
+      <c r="J232" s="20" t="s">
+        <v>1476</v>
+      </c>
+      <c r="K232" s="20">
+        <v>98329</v>
+      </c>
+      <c r="L232" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="M232" s="20">
+        <v>47.385527099999997</v>
+      </c>
+      <c r="N232" s="20">
+        <v>-122.6583272</v>
+      </c>
+      <c r="O232" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="P232" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q232" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="R232" s="20"/>
+      <c r="S232" s="20"/>
+      <c r="T232" s="20"/>
+      <c r="U232" s="20"/>
+      <c r="V232" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="W232" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="X232" s="20" t="s">
+        <v>1338</v>
+      </c>
+      <c r="Y232" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z232" s="20" t="s">
+        <v>1477</v>
+      </c>
+      <c r="AA232" s="20" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AB232" s="20"/>
+      <c r="AC232" s="20" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AD232" s="20"/>
+      <c r="AE232" s="20"/>
+      <c r="AF232" s="20"/>
+      <c r="AG232" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="AH232" s="20" t="s">
+        <v>1480</v>
+      </c>
+      <c r="AI232" s="22"/>
+    </row>
+    <row r="233" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A233" s="20">
+        <v>90236</v>
+      </c>
+      <c r="B233" s="20">
+        <v>21350</v>
+      </c>
+      <c r="C233" s="20"/>
+      <c r="D233" s="20" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E233" s="21">
+        <v>46078</v>
+      </c>
+      <c r="F233" s="20">
+        <v>47</v>
+      </c>
+      <c r="G233" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H233" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I233" s="20" t="s">
+        <v>1484</v>
+      </c>
+      <c r="J233" s="20" t="s">
+        <v>894</v>
+      </c>
+      <c r="K233" s="20">
+        <v>99205</v>
+      </c>
+      <c r="L233" s="20" t="s">
+        <v>894</v>
+      </c>
+      <c r="M233" s="20">
+        <v>47.6794625</v>
+      </c>
+      <c r="N233" s="20">
+        <v>-117.4410869</v>
+      </c>
+      <c r="O233" s="20" t="s">
+        <v>1485</v>
+      </c>
+      <c r="P233" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q233" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="R233" s="20"/>
+      <c r="S233" s="20"/>
+      <c r="T233" s="20"/>
+      <c r="U233" s="20"/>
+      <c r="V233" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="W233" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="X233" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y233" s="20"/>
+      <c r="Z233" s="20" t="s">
+        <v>1486</v>
+      </c>
+      <c r="AA233" s="20" t="s">
+        <v>1482</v>
+      </c>
+      <c r="AB233" s="20"/>
+      <c r="AC233" s="20"/>
+      <c r="AD233" s="20"/>
+      <c r="AE233" s="20"/>
+      <c r="AF233" s="20"/>
+      <c r="AG233" s="20"/>
+      <c r="AH233" s="20"/>
+      <c r="AI233" s="22"/>
+    </row>
+    <row r="234" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A234" s="20">
+        <v>90237</v>
+      </c>
+      <c r="B234" s="20">
+        <v>21262</v>
+      </c>
+      <c r="C234" s="20">
+        <v>1</v>
+      </c>
+      <c r="D234" s="20"/>
+      <c r="E234" s="21">
+        <v>46075</v>
+      </c>
+      <c r="F234" s="20">
+        <v>50</v>
+      </c>
+      <c r="G234" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H234" s="20"/>
+      <c r="I234" s="20" t="s">
+        <v>1488</v>
+      </c>
+      <c r="J234" s="20" t="s">
+        <v>894</v>
+      </c>
+      <c r="K234" s="20">
+        <v>99206</v>
+      </c>
+      <c r="L234" s="20" t="s">
+        <v>894</v>
+      </c>
+      <c r="M234" s="20">
+        <v>47.671650700000001</v>
+      </c>
+      <c r="N234" s="20">
+        <v>-117.2421848</v>
+      </c>
+      <c r="O234" s="20" t="s">
+        <v>1489</v>
+      </c>
+      <c r="P234" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q234" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="R234" s="20"/>
+      <c r="S234" s="20"/>
+      <c r="T234" s="20"/>
+      <c r="U234" s="20"/>
+      <c r="V234" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="W234" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="X234" s="20"/>
+      <c r="Y234" s="20"/>
+      <c r="Z234" s="20" t="s">
+        <v>1490</v>
+      </c>
+      <c r="AA234" s="18" t="s">
+        <v>1491</v>
+      </c>
+      <c r="AB234" s="20"/>
+      <c r="AC234" s="20"/>
+      <c r="AD234" s="20"/>
+      <c r="AE234" s="20"/>
+      <c r="AF234" s="20"/>
+      <c r="AG234" s="20"/>
+      <c r="AH234" s="20"/>
+      <c r="AI234" s="22"/>
+    </row>
+    <row r="235" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H235"/>
     </row>
-    <row r="236" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H236"/>
     </row>
-    <row r="237" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H237"/>
     </row>
-    <row r="238" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H238"/>
     </row>
-    <row r="239" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H239"/>
     </row>
-    <row r="240" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H240"/>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="241" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H241"/>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="242" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H242"/>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="243" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H243"/>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="244" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H244"/>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="245" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H245"/>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="246" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H246"/>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="247" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H247"/>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="248" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H248"/>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="249" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H249"/>
     </row>
   </sheetData>
@@ -21524,11 +21817,12 @@
     <hyperlink ref="AC229" r:id="rId13" xr:uid="{01A2C460-5A5B-400A-98AC-2BF42B651DEC}"/>
     <hyperlink ref="AH230" r:id="rId14" xr:uid="{771FF646-43C9-4E59-85CA-18A328886EF9}"/>
     <hyperlink ref="AA231" r:id="rId15" xr:uid="{F3EA0D7B-FAA2-4DBC-B83D-3E20358359D7}"/>
+    <hyperlink ref="AA234" r:id="rId16" xr:uid="{4A17DC30-A227-48B6-9A34-A1FA1FC7E076}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
+  <pageSetup orientation="portrait" r:id="rId17"/>
   <tableParts count="1">
-    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId18"/>
   </tableParts>
 </worksheet>
 </file>
@@ -21536,13 +21830,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DC9006-39A6-404C-9CCE-6016C38CE417}">
   <dimension ref="A2:Q2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="42.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1294</v>
       </c>
@@ -21601,13 +21895,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82750EAF-E5A3-44AA-9CE9-95763C1F48C5}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.81640625" customWidth="1"/>
+    <col min="1" max="1" width="26.85546875" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1264</v>
       </c>
@@ -21618,7 +21912,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1267</v>
       </c>
@@ -21629,7 +21923,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1269</v>
       </c>
@@ -21640,7 +21934,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1272</v>
       </c>
@@ -21651,7 +21945,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1274</v>
       </c>
@@ -21662,7 +21956,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1276</v>
       </c>
@@ -21673,7 +21967,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1278</v>
       </c>
@@ -21684,7 +21978,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1280</v>
       </c>
@@ -21695,7 +21989,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1317</v>
       </c>
@@ -21717,68 +22011,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04CD9421-3D04-4EA0-825D-6A17750FBC1A}">
   <dimension ref="B4:C19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>1329</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>1319</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C9" s="9" t="s">
         <v>1320</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C10" s="9" t="s">
         <v>1321</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C11" s="9" t="s">
         <v>1322</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C12" s="9" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C13" s="9" t="s">
         <v>1324</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C14" s="9"/>
     </row>
-    <row r="15" spans="2:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:3" ht="18" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
         <v>1325</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
     </row>
-    <row r="17" spans="3:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C17" s="9" t="s">
         <v>1326</v>
       </c>
     </row>
-    <row r="18" spans="3:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:3" ht="18" x14ac:dyDescent="0.25">
       <c r="C18" s="9" t="s">
         <v>1327</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" s="10" t="s">
         <v>1328</v>
       </c>

--- a/Data/Raw/wa_local.xlsx
+++ b/Data/Raw/wa_local.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\WA-FEWP\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E2D2E8-B532-486E-A743-C2A93D2EBEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798C72A6-41DD-4E61-A44C-129D61EBD25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3680" uniqueCount="1492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3695" uniqueCount="1500">
   <si>
     <t>waID</t>
   </si>
@@ -4474,9 +4474,6 @@
     <t>https://www.fox13seattle.com/news/man-shot-killed-federal-way-police</t>
   </si>
   <si>
-    <t xml:space="preserve"> Branden Bouathet  Chindavong</t>
-  </si>
-  <si>
     <t>15941/19905</t>
   </si>
   <si>
@@ -4547,6 +4544,33 @@
   </si>
   <si>
     <t>https://www.spokesman.com/stories/2026/feb/23/spokane-valley-hit-and-run-ends-in-suicide/</t>
+  </si>
+  <si>
+    <t>Deyshawn Joshua Namock</t>
+  </si>
+  <si>
+    <t>River Mile Road</t>
+  </si>
+  <si>
+    <t>Kalama</t>
+  </si>
+  <si>
+    <t>https://www.thereflector.com/stories/sheriffs-office-man-wanted-by-police-appears-to-have-killed-himself-in-cowlitz-county,395514</t>
+  </si>
+  <si>
+    <t>According to police, the subject assaulted a woman, then stole her cell phone and vehicle earlier in the day.  Authorities say he was tracked to a home, but refused to leave.  SWAT was called in and eventually entered the home. Namock was allegedly found dead inside the home, near a gun.</t>
+  </si>
+  <si>
+    <t>Incarcernation links don't work, and the description appears to be wrong</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/CowlitzCountyNewsFirst/posts/1204276338508265/</t>
+  </si>
+  <si>
+    <t>Kelso Police Department; Cowlitz County Sheriff's Office; Lower Columbia SWAT</t>
+  </si>
+  <si>
+    <t>Branden Bouathet  Chindavong</t>
   </si>
 </sst>
 </file>
@@ -4994,8 +5018,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}" name="Table2" displayName="Table2" ref="A1:AI234" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A1:AI234" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}" name="Table2" displayName="Table2" ref="A1:AI235" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A1:AI235" xr:uid="{530C0C3F-276F-472B-8D36-AD238616C20E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:AI219">
     <sortCondition ref="A1:A230"/>
   </sortState>
@@ -18305,7 +18329,7 @@
         <v>90189</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="C186" s="14">
         <v>1</v>
@@ -21232,10 +21256,10 @@
         <v>1444</v>
       </c>
       <c r="AG227" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="AH227" s="20" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="228" spans="1:35" x14ac:dyDescent="0.25">
@@ -21388,7 +21412,7 @@
         <v>20626</v>
       </c>
       <c r="D230" t="s">
-        <v>1467</v>
+        <v>1499</v>
       </c>
       <c r="E230" s="11">
         <v>46059</v>
@@ -21445,7 +21469,7 @@
         <v>1466</v>
       </c>
       <c r="AH230" s="18" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="231" spans="1:35" x14ac:dyDescent="0.25">
@@ -21456,7 +21480,7 @@
         <v>20999</v>
       </c>
       <c r="D231" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E231" s="11">
         <v>46069</v>
@@ -21469,7 +21493,7 @@
       </c>
       <c r="H231"/>
       <c r="I231" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="J231" t="s">
         <v>487</v>
@@ -21505,13 +21529,13 @@
         <v>1338</v>
       </c>
       <c r="Z231" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AA231" s="18" t="s">
         <v>1471</v>
       </c>
-      <c r="AA231" s="18" t="s">
+      <c r="AB231" t="s">
         <v>1472</v>
-      </c>
-      <c r="AB231" t="s">
-        <v>1473</v>
       </c>
     </row>
     <row r="232" spans="1:35" x14ac:dyDescent="0.25">
@@ -21523,7 +21547,7 @@
       </c>
       <c r="C232" s="20"/>
       <c r="D232" s="20" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="E232" s="21">
         <v>46077</v>
@@ -21538,10 +21562,10 @@
         <v>31</v>
       </c>
       <c r="I232" s="20" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="J232" s="20" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="K232" s="20">
         <v>98329</v>
@@ -21581,14 +21605,14 @@
         <v>162</v>
       </c>
       <c r="Z232" s="20" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="AA232" s="20" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="AB232" s="20"/>
       <c r="AC232" s="20" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="AD232" s="20"/>
       <c r="AE232" s="20"/>
@@ -21597,7 +21621,7 @@
         <v>456</v>
       </c>
       <c r="AH232" s="20" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="AI232" s="22"/>
     </row>
@@ -21610,7 +21634,7 @@
       </c>
       <c r="C233" s="20"/>
       <c r="D233" s="20" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="E233" s="21">
         <v>46078</v>
@@ -21625,7 +21649,7 @@
         <v>31</v>
       </c>
       <c r="I233" s="20" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="J233" s="20" t="s">
         <v>894</v>
@@ -21643,7 +21667,7 @@
         <v>-117.4410869</v>
       </c>
       <c r="O233" s="20" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="P233" s="20" t="s">
         <v>36</v>
@@ -21666,10 +21690,10 @@
       </c>
       <c r="Y233" s="20"/>
       <c r="Z233" s="20" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="AA233" s="20" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AB233" s="20"/>
       <c r="AC233" s="20"/>
@@ -21702,7 +21726,7 @@
       </c>
       <c r="H234" s="20"/>
       <c r="I234" s="20" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="J234" s="20" t="s">
         <v>894</v>
@@ -21720,7 +21744,7 @@
         <v>-117.2421848</v>
       </c>
       <c r="O234" s="20" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="P234" s="20" t="s">
         <v>36</v>
@@ -21741,10 +21765,10 @@
       <c r="X234" s="20"/>
       <c r="Y234" s="20"/>
       <c r="Z234" s="20" t="s">
+        <v>1489</v>
+      </c>
+      <c r="AA234" s="18" t="s">
         <v>1490</v>
-      </c>
-      <c r="AA234" s="18" t="s">
-        <v>1491</v>
       </c>
       <c r="AB234" s="20"/>
       <c r="AC234" s="20"/>
@@ -21756,7 +21780,87 @@
       <c r="AI234" s="22"/>
     </row>
     <row r="235" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="H235"/>
+      <c r="A235" s="20">
+        <v>90238</v>
+      </c>
+      <c r="B235" s="20">
+        <v>20739</v>
+      </c>
+      <c r="C235" s="20">
+        <v>1</v>
+      </c>
+      <c r="D235" s="20" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E235" s="21">
+        <v>46049</v>
+      </c>
+      <c r="F235" s="20">
+        <v>25</v>
+      </c>
+      <c r="G235" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H235" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I235" s="20" t="s">
+        <v>1492</v>
+      </c>
+      <c r="J235" s="20" t="s">
+        <v>1493</v>
+      </c>
+      <c r="K235" s="20">
+        <v>98625</v>
+      </c>
+      <c r="L235" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="M235" s="20">
+        <v>46.015679499999997</v>
+      </c>
+      <c r="N235" s="20">
+        <v>-122.8022436</v>
+      </c>
+      <c r="O235" s="20" t="s">
+        <v>1498</v>
+      </c>
+      <c r="P235" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q235" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="R235" s="20"/>
+      <c r="S235" s="20"/>
+      <c r="T235" s="20"/>
+      <c r="U235" s="20"/>
+      <c r="V235" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="W235" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="X235" s="20"/>
+      <c r="Y235" s="20"/>
+      <c r="Z235" s="20" t="s">
+        <v>1495</v>
+      </c>
+      <c r="AA235" s="18" t="s">
+        <v>1494</v>
+      </c>
+      <c r="AB235" s="20" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AC235" s="20" t="s">
+        <v>1497</v>
+      </c>
+      <c r="AD235" s="20"/>
+      <c r="AE235" s="20"/>
+      <c r="AF235" s="20"/>
+      <c r="AG235" s="20"/>
+      <c r="AH235" s="20"/>
+      <c r="AI235" s="22"/>
     </row>
     <row r="236" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H236"/>
@@ -21818,11 +21922,12 @@
     <hyperlink ref="AH230" r:id="rId14" xr:uid="{771FF646-43C9-4E59-85CA-18A328886EF9}"/>
     <hyperlink ref="AA231" r:id="rId15" xr:uid="{F3EA0D7B-FAA2-4DBC-B83D-3E20358359D7}"/>
     <hyperlink ref="AA234" r:id="rId16" xr:uid="{4A17DC30-A227-48B6-9A34-A1FA1FC7E076}"/>
+    <hyperlink ref="AA235" r:id="rId17" xr:uid="{677B4D65-A6C6-4307-9EF7-C343D8230FF9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId18"/>
   <tableParts count="1">
-    <tablePart r:id="rId18"/>
+    <tablePart r:id="rId19"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Data/Raw/wa_local.xlsx
+++ b/Data/Raw/wa_local.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\WA-FEWP\Data\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798C72A6-41DD-4E61-A44C-129D61EBD25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B85035-86BB-4BAF-9A87-1789BCC0BECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2EB8A42E-3B68-4EE6-84B4-49DD96305691}"/>
   </bookViews>
